--- a/Excel Project/Excel Project.xlsx
+++ b/Excel Project/Excel Project.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Mehedi\Desktop\FSDS with Gen AI\FSDS-with-GenAI\Excel Project\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{50A74A1F-962C-4D45-8C9E-8F488E4FDAA0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8F838ACE-CA63-451C-B21E-67EFEEFC926D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11760" activeTab="2" xr2:uid="{9A6DD357-608F-4E40-A02A-0D3B4258E409}"/>
   </bookViews>
@@ -8536,7 +8536,7 @@
           <xdr:spPr>
             <a:xfrm>
               <a:off x="374806" y="1231124"/>
-              <a:ext cx="1370135" cy="1174305"/>
+              <a:ext cx="1383688" cy="1174305"/>
             </a:xfrm>
             <a:prstGeom prst="rect">
               <a:avLst/>
@@ -8614,7 +8614,7 @@
           <xdr:spPr>
             <a:xfrm>
               <a:off x="371475" y="2471713"/>
-              <a:ext cx="1382042" cy="983061"/>
+              <a:ext cx="1395595" cy="983061"/>
             </a:xfrm>
             <a:prstGeom prst="rect">
               <a:avLst/>
@@ -8692,7 +8692,7 @@
           <xdr:spPr>
             <a:xfrm>
               <a:off x="365719" y="3505811"/>
-              <a:ext cx="1395644" cy="1294789"/>
+              <a:ext cx="1409197" cy="1294789"/>
             </a:xfrm>
             <a:prstGeom prst="rect">
               <a:avLst/>
@@ -8770,7 +8770,7 @@
           <xdr:spPr>
             <a:xfrm>
               <a:off x="375904" y="4868089"/>
-              <a:ext cx="1396663" cy="2395004"/>
+              <a:ext cx="1410216" cy="2395004"/>
             </a:xfrm>
             <a:prstGeom prst="rect">
               <a:avLst/>
